--- a/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
@@ -400,139 +400,139 @@
     <t>所有第一版对象均能由GF数据组件查询且没有悬空资源引用。</t>
   </si>
   <si>
+    <t>P0-012</t>
+  </si>
+  <si>
+    <t>框架接入</t>
+  </si>
+  <si>
+    <t>接入项目UI、实体与声音分组</t>
+  </si>
+  <si>
+    <t>扩展UITable、EntityGroupTable与SoundGroupTable并验证安全降级。</t>
+  </si>
+  <si>
+    <t>P0-006,P0-010</t>
+  </si>
+  <si>
+    <t>项目UI、实体和声音能够按配置加载，无资源时不会阻断启动。</t>
+  </si>
+  <si>
+    <t>P0-013</t>
+  </si>
+  <si>
+    <t>集成与阶段验收</t>
+  </si>
+  <si>
+    <t>框架审计</t>
+  </si>
+  <si>
+    <t>建立项目层编译与框架纯度检查入口</t>
+  </si>
+  <si>
+    <t>记录编译、引用、AppConfigs、资源表和audit_framework_purity的检查方式。</t>
+  </si>
+  <si>
+    <t>P0-002,P0-003,P0-006,P0-012</t>
+  </si>
+  <si>
+    <t>项目业务不进入ScriptsBuiltin，框架纯度与启动诊断均可重复执行。</t>
+  </si>
+  <si>
+    <t>P0-014</t>
+  </si>
+  <si>
+    <t>并行美术0 视觉预研</t>
+  </si>
+  <si>
+    <t>ART-G0 视觉基线</t>
+  </si>
+  <si>
+    <t>程序化动作</t>
+  </si>
+  <si>
+    <t>实现程序化动作核心与配置模型</t>
+  </si>
+  <si>
+    <t>实现MotionRig、MotionGraphAsset、强类型参数、稳定节点ID、基础运动原语、顺序／并行／循环／条件组合、集中式MotionExecutor、关节通道所有权和中断策略。</t>
+  </si>
+  <si>
+    <t>P0-002,ART-005</t>
+  </si>
+  <si>
+    <t>ART-MOTION-TOOL</t>
+  </si>
+  <si>
+    <t>Core不依赖GF_X或具体玩法组件；EditMode覆盖配置校验、组合执行、取消恢复和版本迁移；运行热路径无持续GC分配。</t>
+  </si>
+  <si>
+    <t>可视化节点编辑器不在本任务范围；程序集与Hotfix、HybridCLR、FSR边界须在OpenSpec确认后实施。</t>
+  </si>
+  <si>
+    <t>P0-015</t>
+  </si>
+  <si>
+    <t>动作工具</t>
+  </si>
+  <si>
+    <t>建立动作预览、校验与工具包发布链</t>
+  </si>
+  <si>
+    <t>实现Inspector配置、EditMode／PlayMode预览、关节范围Gizmo、模拟参数上下文、静态校验、版本元数据及固定GUID的unitypackage发布流程。</t>
+  </si>
+  <si>
+    <t>ArtResource可安装版本化Core与Editor工具包并预览同一动作资产；缺失关节、参数类型错误、通道冲突和非法连接能够在导出前明确报错。</t>
+  </si>
+  <si>
+    <t>工具包不包含AutoEra Adapter和玩法代码；可视化节点编辑器待代表性样机后决定。</t>
+  </si>
+  <si>
+    <t>P0-016</t>
+  </si>
+  <si>
+    <t>动作贯通</t>
+  </si>
+  <si>
+    <t>完成代表性机器程序动作贯通</t>
+  </si>
+  <si>
+    <t>使用轮式载体、多关节机械臂和可替换效应器，验证待机、移动、转向、瞄准、作业、取消、断电、安全收回、恢复、对象池复用、重进场景和表现LOD。</t>
+  </si>
+  <si>
+    <t>P0-010,P0-012,P0-015,ART-031</t>
+  </si>
+  <si>
+    <t>ART-PILOT</t>
+  </si>
+  <si>
+    <t>美术项目预览与主工程真实状态驱动结果一致；固定GUID、MotionRig绑定和动作资产引用不丢失；停止更新后可从当前玩法状态正确恢复。</t>
+  </si>
+  <si>
+    <t>玩法逻辑拥有结算权威；动作表现不得反向决定产出、任务完成或存档结果。</t>
+  </si>
+  <si>
+    <t>G0-001</t>
+  </si>
+  <si>
+    <t>阶段验收</t>
+  </si>
+  <si>
+    <t>工程基线验收</t>
+  </si>
+  <si>
+    <t>确认Launch启动、Procedure、时间、InputModule、GF.UI、GF.Entity和项目数据共同运行。</t>
+  </si>
+  <si>
+    <t>P0-003,P0-004,P0-005,P0-006,P0-008,P0-009,P0-010,P0-011,P0-012,P0-013</t>
+  </si>
+  <si>
+    <t>G0</t>
+  </si>
+  <si>
+    <t>从Launch进入空业务场景，输入与UI正常，实体可加载，项目表无阻塞错误且未改框架核心。</t>
+  </si>
+  <si>
     <t>未开始</t>
-  </si>
-  <si>
-    <t>P0-012</t>
-  </si>
-  <si>
-    <t>框架接入</t>
-  </si>
-  <si>
-    <t>接入项目UI、实体与声音分组</t>
-  </si>
-  <si>
-    <t>扩展UITable、EntityGroupTable与SoundGroupTable并验证安全降级。</t>
-  </si>
-  <si>
-    <t>P0-006,P0-010</t>
-  </si>
-  <si>
-    <t>项目UI、实体和声音能够按配置加载，无资源时不会阻断启动。</t>
-  </si>
-  <si>
-    <t>P0-013</t>
-  </si>
-  <si>
-    <t>集成与阶段验收</t>
-  </si>
-  <si>
-    <t>框架审计</t>
-  </si>
-  <si>
-    <t>建立项目层编译与框架纯度检查入口</t>
-  </si>
-  <si>
-    <t>记录编译、引用、AppConfigs、资源表和audit_framework_purity的检查方式。</t>
-  </si>
-  <si>
-    <t>P0-002,P0-003,P0-006,P0-012</t>
-  </si>
-  <si>
-    <t>项目业务不进入ScriptsBuiltin，框架纯度与启动诊断均可重复执行。</t>
-  </si>
-  <si>
-    <t>P0-014</t>
-  </si>
-  <si>
-    <t>并行美术0 视觉预研</t>
-  </si>
-  <si>
-    <t>ART-G0 视觉基线</t>
-  </si>
-  <si>
-    <t>程序化动作</t>
-  </si>
-  <si>
-    <t>实现程序化动作核心与配置模型</t>
-  </si>
-  <si>
-    <t>实现MotionRig、MotionGraphAsset、强类型参数、稳定节点ID、基础运动原语、顺序／并行／循环／条件组合、集中式MotionExecutor、关节通道所有权和中断策略。</t>
-  </si>
-  <si>
-    <t>P0-002,ART-005</t>
-  </si>
-  <si>
-    <t>ART-MOTION-TOOL</t>
-  </si>
-  <si>
-    <t>Core不依赖GF_X或具体玩法组件；EditMode覆盖配置校验、组合执行、取消恢复和版本迁移；运行热路径无持续GC分配。</t>
-  </si>
-  <si>
-    <t>可视化节点编辑器不在本任务范围；程序集与Hotfix、HybridCLR、FSR边界须在OpenSpec确认后实施。</t>
-  </si>
-  <si>
-    <t>P0-015</t>
-  </si>
-  <si>
-    <t>动作工具</t>
-  </si>
-  <si>
-    <t>建立动作预览、校验与工具包发布链</t>
-  </si>
-  <si>
-    <t>实现Inspector配置、EditMode／PlayMode预览、关节范围Gizmo、模拟参数上下文、静态校验、版本元数据及固定GUID的unitypackage发布流程。</t>
-  </si>
-  <si>
-    <t>ArtResource可安装版本化Core与Editor工具包并预览同一动作资产；缺失关节、参数类型错误、通道冲突和非法连接能够在导出前明确报错。</t>
-  </si>
-  <si>
-    <t>工具包不包含AutoEra Adapter和玩法代码；可视化节点编辑器待代表性样机后决定。</t>
-  </si>
-  <si>
-    <t>P0-016</t>
-  </si>
-  <si>
-    <t>动作贯通</t>
-  </si>
-  <si>
-    <t>完成代表性机器程序动作贯通</t>
-  </si>
-  <si>
-    <t>使用轮式载体、多关节机械臂和可替换效应器，验证待机、移动、转向、瞄准、作业、取消、断电、安全收回、恢复、对象池复用、重进场景和表现LOD。</t>
-  </si>
-  <si>
-    <t>P0-010,P0-012,P0-015,ART-031</t>
-  </si>
-  <si>
-    <t>ART-PILOT</t>
-  </si>
-  <si>
-    <t>美术项目预览与主工程真实状态驱动结果一致；固定GUID、MotionRig绑定和动作资产引用不丢失；停止更新后可从当前玩法状态正确恢复。</t>
-  </si>
-  <si>
-    <t>玩法逻辑拥有结算权威；动作表现不得反向决定产出、任务完成或存档结果。</t>
-  </si>
-  <si>
-    <t>G0-001</t>
-  </si>
-  <si>
-    <t>阶段验收</t>
-  </si>
-  <si>
-    <t>工程基线验收</t>
-  </si>
-  <si>
-    <t>确认Launch启动、Procedure、时间、InputModule、GF.UI、GF.Entity和项目数据共同运行。</t>
-  </si>
-  <si>
-    <t>P0-003,P0-004,P0-005,P0-006,P0-008,P0-009,P0-010,P0-011,P0-012,P0-013</t>
-  </si>
-  <si>
-    <t>G0</t>
-  </si>
-  <si>
-    <t>从Launch进入空业务场景，输入与UI正常，实体可加载，项目表无阻塞错误且未改框架核心。</t>
   </si>
   <si>
     <t>P1-001</t>
@@ -5926,14 +5926,14 @@
         <v>119</v>
       </c>
       <c r="P12" s="25" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="Q12" s="27"/>
       <c r="R12" s="24"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:18">
       <c r="A13" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>47</v>
@@ -5945,19 +5945,19 @@
         <v>62</v>
       </c>
       <c r="E13" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="G13" s="8" t="s">
         <v>123</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>124</v>
       </c>
       <c r="H13" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>55</v>
@@ -5975,7 +5975,7 @@
         <v>57</v>
       </c>
       <c r="O13" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P13" s="21" t="s">
         <v>59</v>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:18">
       <c r="A14" s="24" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>47</v>
@@ -5994,22 +5994,22 @@
         <v>48</v>
       </c>
       <c r="D14" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="F14" s="24" t="s">
         <v>129</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="G14" s="24" t="s">
         <v>130</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>131</v>
       </c>
       <c r="H14" s="25" t="s">
         <v>53</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>55</v>
@@ -6027,44 +6027,44 @@
         <v>57</v>
       </c>
       <c r="O14" s="24" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P14" s="25" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="27"/>
       <c r="R14" s="24"/>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:18">
       <c r="A15" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="C15" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>62</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="G15" s="8" t="s">
         <v>138</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>139</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I15" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="J15" s="21" t="s">
         <v>140</v>
-      </c>
-      <c r="J15" s="21" t="s">
-        <v>141</v>
       </c>
       <c r="K15" s="22">
         <v>14</v>
@@ -6079,46 +6079,46 @@
         <v>57</v>
       </c>
       <c r="O15" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P15" s="21" t="s">
         <v>59</v>
       </c>
       <c r="Q15" s="23"/>
       <c r="R15" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:18">
       <c r="A16" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B16" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>62</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="G16" s="8" t="s">
         <v>146</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>147</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K16" s="22">
         <v>12</v>
@@ -6133,46 +6133,46 @@
         <v>57</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="P16" s="21" t="s">
         <v>59</v>
       </c>
       <c r="Q16" s="23"/>
       <c r="R16" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:18">
       <c r="A17" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
         <v>152</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>153</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I17" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="J17" s="21" t="s">
         <v>154</v>
-      </c>
-      <c r="J17" s="21" t="s">
-        <v>155</v>
       </c>
       <c r="K17" s="22">
         <v>12</v>
@@ -6187,19 +6187,19 @@
         <v>57</v>
       </c>
       <c r="O17" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P17" s="21" t="s">
         <v>59</v>
       </c>
       <c r="Q17" s="23"/>
       <c r="R17" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:18">
       <c r="A18" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>47</v>
@@ -6208,25 +6208,25 @@
         <v>48</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E18" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="G18" s="8" t="s">
         <v>160</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>161</v>
       </c>
       <c r="H18" s="21" t="s">
         <v>53</v>
       </c>
       <c r="I18" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="J18" s="21" t="s">
-        <v>163</v>
       </c>
       <c r="K18" s="22">
         <v>6</v>
@@ -6241,10 +6241,10 @@
         <v>57</v>
       </c>
       <c r="O18" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="P18" s="21" t="s">
         <v>164</v>
-      </c>
-      <c r="P18" s="21" t="s">
-        <v>120</v>
       </c>
       <c r="Q18" s="23"/>
       <c r="R18" s="8"/>
@@ -6275,7 +6275,7 @@
         <v>53</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J19" s="25" t="s">
         <v>171</v>
@@ -6296,7 +6296,7 @@
         <v>172</v>
       </c>
       <c r="P19" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q19" s="27"/>
       <c r="R19" s="24"/>
@@ -6348,7 +6348,7 @@
         <v>178</v>
       </c>
       <c r="P20" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q20" s="23"/>
       <c r="R20" s="8"/>
@@ -6400,7 +6400,7 @@
         <v>184</v>
       </c>
       <c r="P21" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q21" s="27"/>
       <c r="R21" s="24"/>
@@ -6452,7 +6452,7 @@
         <v>189</v>
       </c>
       <c r="P22" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q22" s="23"/>
       <c r="R22" s="8"/>
@@ -6504,7 +6504,7 @@
         <v>195</v>
       </c>
       <c r="P23" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q23" s="27"/>
       <c r="R23" s="24" t="s">
@@ -6558,7 +6558,7 @@
         <v>200</v>
       </c>
       <c r="P24" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q24" s="23"/>
       <c r="R24" s="8" t="s">
@@ -6612,7 +6612,7 @@
         <v>205</v>
       </c>
       <c r="P25" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q25" s="27"/>
       <c r="R25" s="24" t="s">
@@ -6666,7 +6666,7 @@
         <v>211</v>
       </c>
       <c r="P26" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q26" s="23"/>
       <c r="R26" s="8" t="s">
@@ -6720,7 +6720,7 @@
         <v>217</v>
       </c>
       <c r="P27" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q27" s="27"/>
       <c r="R27" s="24"/>
@@ -6736,10 +6736,10 @@
         <v>167</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>219</v>
@@ -6772,7 +6772,7 @@
         <v>223</v>
       </c>
       <c r="P28" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q28" s="23"/>
       <c r="R28" s="8"/>
@@ -6824,7 +6824,7 @@
         <v>232</v>
       </c>
       <c r="P29" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q29" s="27"/>
       <c r="R29" s="24"/>
@@ -6876,7 +6876,7 @@
         <v>238</v>
       </c>
       <c r="P30" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q30" s="23"/>
       <c r="R30" s="8"/>
@@ -6928,7 +6928,7 @@
         <v>244</v>
       </c>
       <c r="P31" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q31" s="27"/>
       <c r="R31" s="24"/>
@@ -6980,7 +6980,7 @@
         <v>250</v>
       </c>
       <c r="P32" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q32" s="23"/>
       <c r="R32" s="8"/>
@@ -7032,7 +7032,7 @@
         <v>256</v>
       </c>
       <c r="P33" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q33" s="27"/>
       <c r="R33" s="24"/>
@@ -7084,7 +7084,7 @@
         <v>262</v>
       </c>
       <c r="P34" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q34" s="23"/>
       <c r="R34" s="8"/>
@@ -7136,7 +7136,7 @@
         <v>268</v>
       </c>
       <c r="P35" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q35" s="27"/>
       <c r="R35" s="24" t="s">
@@ -7190,7 +7190,7 @@
         <v>274</v>
       </c>
       <c r="P36" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q36" s="23"/>
       <c r="R36" s="8"/>
@@ -7242,7 +7242,7 @@
         <v>280</v>
       </c>
       <c r="P37" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q37" s="27"/>
       <c r="R37" s="24"/>
@@ -7294,7 +7294,7 @@
         <v>286</v>
       </c>
       <c r="P38" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q38" s="23"/>
       <c r="R38" s="8"/>
@@ -7346,7 +7346,7 @@
         <v>292</v>
       </c>
       <c r="P39" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q39" s="27"/>
       <c r="R39" s="24"/>
@@ -7398,7 +7398,7 @@
         <v>299</v>
       </c>
       <c r="P40" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q40" s="23"/>
       <c r="R40" s="8"/>
@@ -7414,10 +7414,10 @@
         <v>226</v>
       </c>
       <c r="D41" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E41" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F41" s="24" t="s">
         <v>301</v>
@@ -7450,7 +7450,7 @@
         <v>305</v>
       </c>
       <c r="P41" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q41" s="27"/>
       <c r="R41" s="24"/>
@@ -7502,7 +7502,7 @@
         <v>314</v>
       </c>
       <c r="P42" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q42" s="23"/>
       <c r="R42" s="8"/>
@@ -7554,7 +7554,7 @@
         <v>320</v>
       </c>
       <c r="P43" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q43" s="27"/>
       <c r="R43" s="24"/>
@@ -7606,7 +7606,7 @@
         <v>326</v>
       </c>
       <c r="P44" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q44" s="23"/>
       <c r="R44" s="8"/>
@@ -7658,7 +7658,7 @@
         <v>331</v>
       </c>
       <c r="P45" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q45" s="27"/>
       <c r="R45" s="24"/>
@@ -7710,7 +7710,7 @@
         <v>337</v>
       </c>
       <c r="P46" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q46" s="23"/>
       <c r="R46" s="8"/>
@@ -7762,7 +7762,7 @@
         <v>343</v>
       </c>
       <c r="P47" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q47" s="27"/>
       <c r="R47" s="24" t="s">
@@ -7816,7 +7816,7 @@
         <v>349</v>
       </c>
       <c r="P48" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q48" s="23"/>
       <c r="R48" s="8"/>
@@ -7868,7 +7868,7 @@
         <v>355</v>
       </c>
       <c r="P49" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q49" s="27"/>
       <c r="R49" s="24"/>
@@ -7920,7 +7920,7 @@
         <v>361</v>
       </c>
       <c r="P50" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q50" s="23"/>
       <c r="R50" s="8"/>
@@ -7972,7 +7972,7 @@
         <v>367</v>
       </c>
       <c r="P51" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q51" s="27"/>
       <c r="R51" s="24"/>
@@ -8024,7 +8024,7 @@
         <v>372</v>
       </c>
       <c r="P52" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q52" s="23"/>
       <c r="R52" s="8"/>
@@ -8076,7 +8076,7 @@
         <v>378</v>
       </c>
       <c r="P53" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q53" s="27"/>
       <c r="R53" s="24"/>
@@ -8128,7 +8128,7 @@
         <v>384</v>
       </c>
       <c r="P54" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q54" s="23"/>
       <c r="R54" s="8"/>
@@ -8180,7 +8180,7 @@
         <v>390</v>
       </c>
       <c r="P55" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q55" s="27"/>
       <c r="R55" s="24"/>
@@ -8232,7 +8232,7 @@
         <v>396</v>
       </c>
       <c r="P56" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q56" s="23"/>
       <c r="R56" s="8"/>
@@ -8248,10 +8248,10 @@
         <v>308</v>
       </c>
       <c r="D57" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E57" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F57" s="24" t="s">
         <v>398</v>
@@ -8284,7 +8284,7 @@
         <v>402</v>
       </c>
       <c r="P57" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q57" s="27"/>
       <c r="R57" s="24"/>
@@ -8336,7 +8336,7 @@
         <v>411</v>
       </c>
       <c r="P58" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q58" s="23"/>
       <c r="R58" s="8" t="s">
@@ -8390,7 +8390,7 @@
         <v>417</v>
       </c>
       <c r="P59" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q59" s="27"/>
       <c r="R59" s="24" t="s">
@@ -8444,7 +8444,7 @@
         <v>421</v>
       </c>
       <c r="P60" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q60" s="23"/>
       <c r="R60" s="8" t="s">
@@ -8498,7 +8498,7 @@
         <v>426</v>
       </c>
       <c r="P61" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q61" s="27"/>
       <c r="R61" s="24" t="s">
@@ -8552,7 +8552,7 @@
         <v>431</v>
       </c>
       <c r="P62" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q62" s="23"/>
       <c r="R62" s="8"/>
@@ -8604,7 +8604,7 @@
         <v>436</v>
       </c>
       <c r="P63" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q63" s="27"/>
       <c r="R63" s="24" t="s">
@@ -8658,7 +8658,7 @@
         <v>442</v>
       </c>
       <c r="P64" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q64" s="23"/>
       <c r="R64" s="8"/>
@@ -8710,7 +8710,7 @@
         <v>447</v>
       </c>
       <c r="P65" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q65" s="27"/>
       <c r="R65" s="24" t="s">
@@ -8764,7 +8764,7 @@
         <v>452</v>
       </c>
       <c r="P66" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q66" s="23"/>
       <c r="R66" s="8" t="s">
@@ -8818,7 +8818,7 @@
         <v>458</v>
       </c>
       <c r="P67" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q67" s="27"/>
       <c r="R67" s="24"/>
@@ -8870,7 +8870,7 @@
         <v>463</v>
       </c>
       <c r="P68" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q68" s="23"/>
       <c r="R68" s="8"/>
@@ -8922,7 +8922,7 @@
         <v>469</v>
       </c>
       <c r="P69" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q69" s="27"/>
       <c r="R69" s="24"/>
@@ -8974,7 +8974,7 @@
         <v>475</v>
       </c>
       <c r="P70" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q70" s="23"/>
       <c r="R70" s="8"/>
@@ -9026,7 +9026,7 @@
         <v>481</v>
       </c>
       <c r="P71" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q71" s="27"/>
       <c r="R71" s="24" t="s">
@@ -9080,7 +9080,7 @@
         <v>487</v>
       </c>
       <c r="P72" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q72" s="23"/>
       <c r="R72" s="8"/>
@@ -9132,7 +9132,7 @@
         <v>493</v>
       </c>
       <c r="P73" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q73" s="27"/>
       <c r="R73" s="24"/>
@@ -9184,7 +9184,7 @@
         <v>499</v>
       </c>
       <c r="P74" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q74" s="23"/>
       <c r="R74" s="8" t="s">
@@ -9202,10 +9202,10 @@
         <v>405</v>
       </c>
       <c r="D75" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E75" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F75" s="24" t="s">
         <v>501</v>
@@ -9238,7 +9238,7 @@
         <v>505</v>
       </c>
       <c r="P75" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q75" s="27"/>
       <c r="R75" s="24"/>
@@ -9290,7 +9290,7 @@
         <v>514</v>
       </c>
       <c r="P76" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q76" s="23"/>
       <c r="R76" s="8"/>
@@ -9342,7 +9342,7 @@
         <v>520</v>
       </c>
       <c r="P77" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q77" s="27"/>
       <c r="R77" s="24"/>
@@ -9394,7 +9394,7 @@
         <v>526</v>
       </c>
       <c r="P78" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q78" s="23"/>
       <c r="R78" s="8"/>
@@ -9446,7 +9446,7 @@
         <v>532</v>
       </c>
       <c r="P79" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q79" s="27"/>
       <c r="R79" s="24"/>
@@ -9498,7 +9498,7 @@
         <v>538</v>
       </c>
       <c r="P80" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q80" s="23"/>
       <c r="R80" s="8"/>
@@ -9550,7 +9550,7 @@
         <v>544</v>
       </c>
       <c r="P81" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q81" s="27"/>
       <c r="R81" s="24"/>
@@ -9602,7 +9602,7 @@
         <v>550</v>
       </c>
       <c r="P82" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q82" s="23"/>
       <c r="R82" s="8"/>
@@ -9654,7 +9654,7 @@
         <v>556</v>
       </c>
       <c r="P83" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q83" s="27"/>
       <c r="R83" s="24"/>
@@ -9706,7 +9706,7 @@
         <v>562</v>
       </c>
       <c r="P84" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q84" s="23"/>
       <c r="R84" s="8"/>
@@ -9758,7 +9758,7 @@
         <v>568</v>
       </c>
       <c r="P85" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q85" s="27"/>
       <c r="R85" s="24"/>
@@ -9810,7 +9810,7 @@
         <v>574</v>
       </c>
       <c r="P86" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q86" s="23"/>
       <c r="R86" s="8"/>
@@ -9862,7 +9862,7 @@
         <v>580</v>
       </c>
       <c r="P87" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q87" s="27"/>
       <c r="R87" s="24"/>
@@ -9914,7 +9914,7 @@
         <v>585</v>
       </c>
       <c r="P88" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q88" s="23"/>
       <c r="R88" s="8"/>
@@ -9966,7 +9966,7 @@
         <v>591</v>
       </c>
       <c r="P89" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q89" s="27"/>
       <c r="R89" s="24"/>
@@ -9982,10 +9982,10 @@
         <v>508</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>593</v>
@@ -10018,7 +10018,7 @@
         <v>597</v>
       </c>
       <c r="P90" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q90" s="23"/>
       <c r="R90" s="8"/>
@@ -10070,7 +10070,7 @@
         <v>606</v>
       </c>
       <c r="P91" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q91" s="27"/>
       <c r="R91" s="24" t="s">
@@ -10124,7 +10124,7 @@
         <v>612</v>
       </c>
       <c r="P92" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q92" s="23"/>
       <c r="R92" s="8" t="s">
@@ -10178,7 +10178,7 @@
         <v>618</v>
       </c>
       <c r="P93" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q93" s="27"/>
       <c r="R93" s="24"/>
@@ -10230,7 +10230,7 @@
         <v>623</v>
       </c>
       <c r="P94" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q94" s="23"/>
       <c r="R94" s="8"/>
@@ -10282,7 +10282,7 @@
         <v>629</v>
       </c>
       <c r="P95" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q95" s="27"/>
       <c r="R95" s="24"/>
@@ -10334,7 +10334,7 @@
         <v>635</v>
       </c>
       <c r="P96" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q96" s="23"/>
       <c r="R96" s="8" t="s">
@@ -10388,7 +10388,7 @@
         <v>641</v>
       </c>
       <c r="P97" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q97" s="27"/>
       <c r="R97" s="24" t="s">
@@ -10442,7 +10442,7 @@
         <v>647</v>
       </c>
       <c r="P98" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q98" s="23"/>
       <c r="R98" s="8"/>
@@ -10494,7 +10494,7 @@
         <v>653</v>
       </c>
       <c r="P99" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q99" s="27"/>
       <c r="R99" s="24" t="s">
@@ -10548,7 +10548,7 @@
         <v>658</v>
       </c>
       <c r="P100" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q100" s="23"/>
       <c r="R100" s="8"/>
@@ -10600,7 +10600,7 @@
         <v>664</v>
       </c>
       <c r="P101" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q101" s="27"/>
       <c r="R101" s="24"/>
@@ -10652,7 +10652,7 @@
         <v>670</v>
       </c>
       <c r="P102" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q102" s="23"/>
       <c r="R102" s="8"/>
@@ -10704,7 +10704,7 @@
         <v>676</v>
       </c>
       <c r="P103" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q103" s="27"/>
       <c r="R103" s="24" t="s">
@@ -10758,7 +10758,7 @@
         <v>682</v>
       </c>
       <c r="P104" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q104" s="23"/>
       <c r="R104" s="8" t="s">
@@ -10776,10 +10776,10 @@
         <v>600</v>
       </c>
       <c r="D105" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E105" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F105" s="24" t="s">
         <v>684</v>
@@ -10812,7 +10812,7 @@
         <v>688</v>
       </c>
       <c r="P105" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q105" s="27"/>
       <c r="R105" s="24"/>
@@ -10864,7 +10864,7 @@
         <v>697</v>
       </c>
       <c r="P106" s="21" t="s">
-        <v>120</v>
+        <v>59</v>
       </c>
       <c r="Q106" s="23"/>
       <c r="R106" s="8"/>
@@ -10916,7 +10916,7 @@
         <v>701</v>
       </c>
       <c r="P107" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q107" s="27"/>
       <c r="R107" s="24"/>
@@ -10968,7 +10968,7 @@
         <v>706</v>
       </c>
       <c r="P108" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q108" s="23"/>
       <c r="R108" s="8"/>
@@ -11020,7 +11020,7 @@
         <v>711</v>
       </c>
       <c r="P109" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q109" s="27"/>
       <c r="R109" s="24"/>
@@ -11072,7 +11072,7 @@
         <v>716</v>
       </c>
       <c r="P110" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q110" s="23"/>
       <c r="R110" s="8" t="s">
@@ -11126,7 +11126,7 @@
         <v>721</v>
       </c>
       <c r="P111" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q111" s="27"/>
       <c r="R111" s="24"/>
@@ -11178,7 +11178,7 @@
         <v>727</v>
       </c>
       <c r="P112" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q112" s="23"/>
       <c r="R112" s="8"/>
@@ -11230,7 +11230,7 @@
         <v>732</v>
       </c>
       <c r="P113" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q113" s="27"/>
       <c r="R113" s="24"/>
@@ -11282,7 +11282,7 @@
         <v>737</v>
       </c>
       <c r="P114" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q114" s="23"/>
       <c r="R114" s="8"/>
@@ -11334,7 +11334,7 @@
         <v>743</v>
       </c>
       <c r="P115" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q115" s="27"/>
       <c r="R115" s="24"/>
@@ -11386,7 +11386,7 @@
         <v>749</v>
       </c>
       <c r="P116" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q116" s="23"/>
       <c r="R116" s="8"/>
@@ -11438,7 +11438,7 @@
         <v>755</v>
       </c>
       <c r="P117" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q117" s="27"/>
       <c r="R117" s="24"/>
@@ -11454,10 +11454,10 @@
         <v>691</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>757</v>
@@ -11490,7 +11490,7 @@
         <v>761</v>
       </c>
       <c r="P118" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q118" s="23"/>
       <c r="R118" s="8"/>
@@ -11542,7 +11542,7 @@
         <v>770</v>
       </c>
       <c r="P119" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q119" s="27"/>
       <c r="R119" s="24"/>
@@ -11594,7 +11594,7 @@
         <v>776</v>
       </c>
       <c r="P120" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q120" s="23"/>
       <c r="R120" s="8" t="s">
@@ -11648,7 +11648,7 @@
         <v>782</v>
       </c>
       <c r="P121" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q121" s="27"/>
       <c r="R121" s="24"/>
@@ -11700,7 +11700,7 @@
         <v>788</v>
       </c>
       <c r="P122" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q122" s="23"/>
       <c r="R122" s="8"/>
@@ -11752,7 +11752,7 @@
         <v>794</v>
       </c>
       <c r="P123" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q123" s="27"/>
       <c r="R123" s="24"/>
@@ -11804,7 +11804,7 @@
         <v>800</v>
       </c>
       <c r="P124" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q124" s="23"/>
       <c r="R124" s="8"/>
@@ -11856,7 +11856,7 @@
         <v>806</v>
       </c>
       <c r="P125" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q125" s="27"/>
       <c r="R125" s="24"/>
@@ -11908,7 +11908,7 @@
         <v>813</v>
       </c>
       <c r="P126" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q126" s="23"/>
       <c r="R126" s="8"/>
@@ -11960,7 +11960,7 @@
         <v>819</v>
       </c>
       <c r="P127" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q127" s="27"/>
       <c r="R127" s="24"/>
@@ -12012,7 +12012,7 @@
         <v>825</v>
       </c>
       <c r="P128" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q128" s="23"/>
       <c r="R128" s="8"/>
@@ -12064,7 +12064,7 @@
         <v>831</v>
       </c>
       <c r="P129" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q129" s="27"/>
       <c r="R129" s="24"/>
@@ -12116,7 +12116,7 @@
         <v>837</v>
       </c>
       <c r="P130" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q130" s="23"/>
       <c r="R130" s="8"/>
@@ -12132,7 +12132,7 @@
         <v>764</v>
       </c>
       <c r="D131" s="24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E131" s="24" t="s">
         <v>839</v>
@@ -12168,7 +12168,7 @@
         <v>843</v>
       </c>
       <c r="P131" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q131" s="27"/>
       <c r="R131" s="24" t="s">
@@ -12186,7 +12186,7 @@
         <v>764</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>845</v>
@@ -12222,7 +12222,7 @@
         <v>848</v>
       </c>
       <c r="P132" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q132" s="23"/>
       <c r="R132" s="8"/>
@@ -12232,10 +12232,10 @@
         <v>849</v>
       </c>
       <c r="B133" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="C133" s="24" t="s">
         <v>135</v>
-      </c>
-      <c r="C133" s="24" t="s">
-        <v>136</v>
       </c>
       <c r="D133" s="24" t="s">
         <v>850</v>
@@ -12288,10 +12288,10 @@
         <v>857</v>
       </c>
       <c r="B134" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C134" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D134" s="8" t="s">
         <v>850</v>
@@ -12344,10 +12344,10 @@
         <v>863</v>
       </c>
       <c r="B135" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C135" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C135" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D135" s="8" t="s">
         <v>864</v>
@@ -12400,10 +12400,10 @@
         <v>869</v>
       </c>
       <c r="B136" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C136" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D136" s="8" t="s">
         <v>870</v>
@@ -12454,10 +12454,10 @@
         <v>877</v>
       </c>
       <c r="B137" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C137" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C137" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D137" s="8" t="s">
         <v>878</v>
@@ -12508,10 +12508,10 @@
         <v>884</v>
       </c>
       <c r="B138" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C138" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C138" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D138" s="8" t="s">
         <v>885</v>
@@ -12560,10 +12560,10 @@
         <v>890</v>
       </c>
       <c r="B139" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C139" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D139" s="8" t="s">
         <v>850</v>
@@ -12602,7 +12602,7 @@
         <v>895</v>
       </c>
       <c r="P139" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q139" s="23"/>
       <c r="R139" s="8"/>
@@ -12612,10 +12612,10 @@
         <v>896</v>
       </c>
       <c r="B140" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C140" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D140" s="8" t="s">
         <v>897</v>
@@ -12636,7 +12636,7 @@
         <v>901</v>
       </c>
       <c r="J140" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K140" s="22">
         <v>8</v>
@@ -12654,7 +12654,7 @@
         <v>902</v>
       </c>
       <c r="P140" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q140" s="23"/>
       <c r="R140" s="8" t="s">
@@ -12666,10 +12666,10 @@
         <v>904</v>
       </c>
       <c r="B141" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C141" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C141" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D141" s="8" t="s">
         <v>897</v>
@@ -12690,7 +12690,7 @@
         <v>908</v>
       </c>
       <c r="J141" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K141" s="22">
         <v>8</v>
@@ -12708,7 +12708,7 @@
         <v>909</v>
       </c>
       <c r="P141" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q141" s="23"/>
       <c r="R141" s="8" t="s">
@@ -12720,10 +12720,10 @@
         <v>911</v>
       </c>
       <c r="B142" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="C142" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="D142" s="8" t="s">
         <v>897</v>
@@ -12762,7 +12762,7 @@
         <v>917</v>
       </c>
       <c r="P142" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q142" s="23"/>
       <c r="R142" s="8"/>
@@ -12814,7 +12814,7 @@
         <v>925</v>
       </c>
       <c r="P143" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q143" s="23"/>
       <c r="R143" s="8"/>
@@ -12866,7 +12866,7 @@
         <v>930</v>
       </c>
       <c r="P144" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q144" s="23"/>
       <c r="R144" s="8"/>
@@ -12918,7 +12918,7 @@
         <v>935</v>
       </c>
       <c r="P145" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q145" s="23"/>
       <c r="R145" s="8"/>
@@ -12970,7 +12970,7 @@
         <v>941</v>
       </c>
       <c r="P146" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q146" s="23"/>
       <c r="R146" s="8"/>
@@ -13022,7 +13022,7 @@
         <v>950</v>
       </c>
       <c r="P147" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q147" s="23"/>
       <c r="R147" s="8"/>
@@ -13074,7 +13074,7 @@
         <v>955</v>
       </c>
       <c r="P148" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q148" s="23"/>
       <c r="R148" s="8"/>
@@ -13126,7 +13126,7 @@
         <v>960</v>
       </c>
       <c r="P149" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q149" s="23"/>
       <c r="R149" s="8" t="s">
@@ -13180,7 +13180,7 @@
         <v>964</v>
       </c>
       <c r="P150" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q150" s="23"/>
       <c r="R150" s="8"/>
@@ -13232,7 +13232,7 @@
         <v>969</v>
       </c>
       <c r="P151" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q151" s="23"/>
       <c r="R151" s="8" t="s">
@@ -13286,7 +13286,7 @@
         <v>973</v>
       </c>
       <c r="P152" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q152" s="23"/>
       <c r="R152" s="8" t="s">
@@ -13340,7 +13340,7 @@
         <v>980</v>
       </c>
       <c r="P153" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q153" s="23"/>
       <c r="R153" s="8" t="s">
@@ -13394,7 +13394,7 @@
         <v>986</v>
       </c>
       <c r="P154" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q154" s="23"/>
       <c r="R154" s="8"/>
@@ -13446,7 +13446,7 @@
         <v>993</v>
       </c>
       <c r="P155" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q155" s="23"/>
       <c r="R155" s="8"/>
@@ -13498,7 +13498,7 @@
         <v>999</v>
       </c>
       <c r="P156" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q156" s="23"/>
       <c r="R156" s="8"/>
@@ -13550,7 +13550,7 @@
         <v>1005</v>
       </c>
       <c r="P157" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q157" s="23"/>
       <c r="R157" s="8" t="s">
@@ -13604,7 +13604,7 @@
         <v>1010</v>
       </c>
       <c r="P158" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q158" s="23"/>
       <c r="R158" s="8" t="s">
@@ -13658,7 +13658,7 @@
         <v>1016</v>
       </c>
       <c r="P159" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q159" s="23"/>
       <c r="R159" s="8" t="s">
@@ -13712,7 +13712,7 @@
         <v>1022</v>
       </c>
       <c r="P160" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q160" s="23"/>
       <c r="R160" s="8" t="s">
@@ -13766,7 +13766,7 @@
         <v>1027</v>
       </c>
       <c r="P161" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q161" s="23"/>
       <c r="R161" s="8"/>
@@ -13818,7 +13818,7 @@
         <v>1034</v>
       </c>
       <c r="P162" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q162" s="23"/>
       <c r="R162" s="8"/>
@@ -13870,7 +13870,7 @@
         <v>1041</v>
       </c>
       <c r="P163" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q163" s="23"/>
       <c r="R163" s="8"/>
@@ -13922,7 +13922,7 @@
         <v>1048</v>
       </c>
       <c r="P164" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q164" s="23"/>
       <c r="R164" s="8" t="s">
@@ -13976,7 +13976,7 @@
         <v>1055</v>
       </c>
       <c r="P165" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q165" s="23"/>
       <c r="R165" s="8" t="s">
@@ -14030,7 +14030,7 @@
         <v>1061</v>
       </c>
       <c r="P166" s="21" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q166" s="23"/>
       <c r="R166" s="8"/>
@@ -14082,7 +14082,7 @@
         <v>1067</v>
       </c>
       <c r="P167" s="8" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q167" s="31"/>
       <c r="R167" s="8"/>
@@ -14134,7 +14134,7 @@
         <v>1073</v>
       </c>
       <c r="P168" s="8" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q168" s="31"/>
       <c r="R168" s="8"/>
@@ -14186,7 +14186,7 @@
         <v>1080</v>
       </c>
       <c r="P169" s="8" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q169" s="31"/>
       <c r="R169" s="8"/>
@@ -14202,7 +14202,7 @@
         <v>764</v>
       </c>
       <c r="D170" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E170" s="8" t="s">
         <v>1075</v>
@@ -14238,7 +14238,7 @@
         <v>1086</v>
       </c>
       <c r="P170" s="8" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q170" s="31"/>
       <c r="R170" s="8"/>
@@ -14286,7 +14286,7 @@
         <v>1092</v>
       </c>
       <c r="P171" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q171" s="27"/>
       <c r="R171" s="24" t="s">
@@ -14336,7 +14336,7 @@
         <v>1098</v>
       </c>
       <c r="P172" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q172" s="27"/>
       <c r="R172" s="24" t="s">
@@ -14386,7 +14386,7 @@
         <v>1103</v>
       </c>
       <c r="P173" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q173" s="27"/>
       <c r="R173" s="24" t="s">
@@ -14436,7 +14436,7 @@
         <v>1109</v>
       </c>
       <c r="P174" s="25" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="Q174" s="27"/>
       <c r="R174" s="24" t="s">
@@ -14523,10 +14523,10 @@
         <v>166</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -14739,10 +14739,10 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7">
       <c r="A11" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>135</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>136</v>
       </c>
       <c r="C11" s="8">
         <f>COUNTIF(开发任务!$B$2:$B$174,A11)</f>
@@ -14949,7 +14949,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B6" s="8">
         <f>COUNTIF(开发任务!$D$2:$D$174,A6)</f>
@@ -15553,7 +15553,7 @@
     </row>
     <row r="5" ht="56" customHeight="1" spans="1:6">
       <c r="A5" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>1188</v>

--- a/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
@@ -4422,7 +4422,11 @@
         </is>
       </c>
       <c r="Q32" s="33" t="n"/>
-      <c r="R32" s="8" t="n"/>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t>**队列容量与溢出规则已确认**（《机器自动化与算法》§队列容量与溢出、DEC-102）：机器任务队列 32、效应器行为队列 16、算力等待队列 64、算法实例瞬时事件队列 32、通信接收器有效请求记录 64；满时拒绝新内容并返回「队列已满」，不丢弃、不覆盖、不驱逐。实现时需同时暴露**占用率与最近拒绝次数**——警报目录里的 ALERT_QUEUE_WARNING（75%·提醒）与ALERT_QUEUE_SATURATED（100%·严重）以及中枢／诊断界面的占用显示都依赖它们。见 Docs/GameDesign/02-系统设计/15-警报系统.md。</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="24" customHeight="1" s="1">
       <c r="A33" s="24" t="inlineStr">
@@ -9324,7 +9328,8 @@
       <c r="Q92" s="33" t="n"/>
       <c r="R92" s="8" t="inlineStr">
         <is>
-          <t>2026-09-10设计同步，未据此变更实现状态。</t>
+          <t>2026-09-10设计同步，未据此变更实现状态。
+2026-09-21 **图纸内容来源已补齐**：`Docs/GameDesign/02-系统设计/04-建筑与建造.md` 新增「第一版图纸清单」（类型／名称／解锁条件／可建数量限制／成本与时间出处），并定下口径——除清单中明确限制的条目外一律不限（工坊 1 座、初始太阳能不可新建）。仍待确认：第二台生物质发电机是否需要图纸与其台数上限、三段传送带的成本与施工时间（留给 P6-015）。本行 DoD 的「未得图纸不能建造」现在有完整目录可依据。见 DEC-200。</t>
         </is>
       </c>
     </row>
@@ -10061,7 +10066,8 @@
       <c r="Q101" s="34" t="n"/>
       <c r="R101" s="24" t="inlineStr">
         <is>
-          <t>**警报域已经能报、能合并、能恢复**：新增三级警报（提醒／警告／严重）、警报账本与区域监视器。合并规则按规格做成「一行一问题」——条件持续存在期间**零写入**，次数是「发生过的段数」而不是轮询次数（否则一条整夜停机就能把次数刷到几万）；恢复由**真实条件**决定并转历史，再次发生则同一行重新活跃、次数 +1；界面侧只开放「标记已读」，账本不提供清除接口（规格：无手动清除故障按钮）。第一批四类：缺电停机、电量耗尽、燃料耗尽、机器完全损坏——队列溢出与算法异常**不做**，它们各自的判据还没落定，凭猜的阈值报警等于让玩家白跑。责任对象名已经能解析（机器取花名册名），警报也写进了事件日志。仍未接：警报界面（P6-012）、HUD 警报摘要、中枢三处的警报栏、快捷定位。见 openspec/changes/alert-system。</t>
+          <t>**警报域已经能报、能合并、能恢复**：新增三级警报（提醒／警告／严重）、警报账本与区域监视器。合并规则按规格做成「一行一问题」——条件持续存在期间**零写入**，次数是「发生过的段数」而不是轮询次数（否则一条整夜停机就能把次数刷到几万）；恢复由**真实条件**决定并转历史，再次发生则同一行重新活跃、次数 +1；界面侧只开放「标记已读」，账本不提供清除接口（规格：无手动清除故障按钮）。第一批四类：缺电停机、电量耗尽、燃料耗尽、机器完全损坏——队列溢出与算法异常**不做**，它们各自的判据还没落定，凭猜的阈值报警等于让玩家白跑。责任对象名已经能解析（机器取花名册名），警报也写进了事件日志。仍未接：警报界面（P6-012）、HUD 警报摘要、中枢三处的警报栏、快捷定位。见 openspec/changes/alert-system。
+2026-09-21 **【更正】上一批备注里「队列溢出与算法异常缺判据」是错的**：判据早已存在——队列容量、拒绝规则、75%／100% 两档预警、合并计数、主要来源与最近拒绝次数见《机器自动化与算法》§队列容量与溢出与 DEC-102；算法变红边界见 DEC-104。真正缺的是一份**警报目录**，现已补齐：`Docs/GameDesign/02-系统设计/15-警报系统.md`（17 条，逐条给等级／来源／触发判据出处／真实恢复条件，并明确「警报」与「能源历史」是两条通道），文案表补 ALERT_QUEUE_WARNING／ALERT_QUEUE_SATURATED，决策记录见 DEC-199／DEC-201。同时发现批次 18 自造的四类警报不在目录内，整改清单记在 openspec/changes/alert-system 第 8 节，与警报界面接线同批或同批之后执行。</t>
         </is>
       </c>
     </row>
@@ -10229,7 +10235,8 @@
       <c r="Q103" s="34" t="n"/>
       <c r="R103" s="24" t="inlineStr">
         <is>
-          <t>2026-09-10设计同步，未据此变更实现状态。</t>
+          <t>2026-09-10设计同步，未据此变更实现状态。
+2026-09-21 **录入所需的目录已经就位**：图纸清单见《建筑与建造》，警报目录与等级映射见《警报系统》，队列警报的两条文案已补进《玩家可见文案规格》。录入时按目录逐条对齐，不再需要自行挑选内容。见 DEC-199／DEC-200。</t>
         </is>
       </c>
     </row>

--- a/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
+++ b/Docs/GameDesign/05-开发计划/第一版开发任务表.xlsx
@@ -3688,13 +3688,13 @@
       </c>
       <c r="P23" s="25" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q23" s="34" t="n"/>
       <c r="R23" s="24" t="inlineStr">
         <is>
-          <t>RegionWorkQueue已建，作业点申请与等待队列待补全</t>
+          <t>审计完成：申请/排队/占用/释放/取消/销毁对称路径已被4个测试文件覆盖；补2个真实缺口(等待者优先级升级+MotionWorkBridge WorkState跟随队列)；回归InitialRegion6/6+MotionWorkBridge5/5+MachineRegionIdentity13/13+MachineNavigation15/15+QA边界4/4全绿</t>
         </is>
       </c>
     </row>
@@ -4944,13 +4944,13 @@
       </c>
       <c r="P38" s="21" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q38" s="33" t="n"/>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>MachineRoster已建，中枢机器列表状态摘要UI待补全</t>
+          <t>中枢机器索引只列已部署机器(库中蓝图移出)+运行时详情(任务/算力/导航/算法实例)已接入；MachineReadModel 12/12；总览页三栏聚合属P6-009</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       <c r="Q40" s="33" t="n"/>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>移动/选中反馈已部分实现，状态基础反馈待补全</t>
+          <t>程序部分已交付：选中轮廓(RegionInputModule.SetHighlight)+轮组运动(MachineNavigationMotionAdapter)；激活灯/断电/等待VFX表现待美术批次验收</t>
         </is>
       </c>
     </row>
@@ -6032,11 +6032,15 @@
       </c>
       <c r="P51" s="25" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q51" s="34" t="n"/>
-      <c r="R51" s="24" t="n"/>
+      <c r="R51" s="24" t="inlineStr">
+        <is>
+          <t>B20-B30+b32+b33全链路交付：画布节点/端口/边元素渲染、节点库(目录+搜索+分类)、两步强类型连线、选边/选节点删除(级联)、网格落位、拖拽回写、8字段绑定齐全；测试：服务13/13+读模型32/32+绑定3/3+PlayMode端到端1/1全绿</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="24" customHeight="1" s="1">
       <c r="A52" s="8" t="inlineStr">
@@ -6112,11 +6116,15 @@
       </c>
       <c r="P52" s="21" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q52" s="33" t="n"/>
-      <c r="R52" s="8" t="n"/>
+      <c r="R52" s="8" t="inlineStr">
+        <is>
+          <t>B20/B21/B29+b32+b33全链路交付：节点库(20种类中文目录+搜索过滤+分类状态)、检查器/问题栏随命令经Changed事件同步刷新、端口连接态展示、校验问题定位；测试全绿(见P3-010备注)</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="24" customHeight="1" s="1">
       <c r="A53" s="24" t="inlineStr">
@@ -6192,11 +6200,15 @@
       </c>
       <c r="P53" s="25" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q53" s="34" t="n"/>
-      <c r="R53" s="24" t="n"/>
+      <c r="R53" s="24" t="inlineStr">
+        <is>
+          <t>B22/B23库浏览与实例化、B26/B27应用与警告确认、B28组件选择器已交付(读模型测试28/28)</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="24" customHeight="1" s="1">
       <c r="A54" s="8" t="inlineStr">
@@ -6356,11 +6368,15 @@
       </c>
       <c r="P55" s="25" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q55" s="34" t="n"/>
-      <c r="R55" s="24" t="n"/>
+      <c r="R55" s="24" t="inlineStr">
+        <is>
+          <t>B21执行路径高亮(已执行/失败节点标记)与B31诊断按值细节(当时值vs默认值)已交付</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="25.5" customHeight="1" s="1">
       <c r="A56" s="8" t="inlineStr">
@@ -6436,11 +6452,15 @@
       </c>
       <c r="P56" s="21" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q56" s="33" t="n"/>
-      <c r="R56" s="8" t="n"/>
+      <c r="R56" s="8" t="inlineStr">
+        <is>
+          <t>五套系统模板按DEC-202成本定稿经InitialAlgorithmTemplates.Seed接入WorldSession</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="24" customHeight="1" s="1">
       <c r="A57" s="24" t="inlineStr">
@@ -10092,11 +10112,15 @@
       </c>
       <c r="P101" s="25" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="Q101" s="34" t="n"/>
-      <c r="R101" s="24" t="n"/>
+      <c r="R101" s="24" t="inlineStr">
+        <is>
+          <t>三级警报/同源合并/恢复转历史/排序已交付并测试(AutoEraAlertService+RegionAlertMonitor 9/9+9/9)；读模型Source身份补齐供定位；AlertForm接线(列表/详情/标记已读/定位/筛选/空与不可用状态)，预制体4按钮绑定回写，NOT_WIRED双侧移除</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
@@ -10172,11 +10196,15 @@
       </c>
       <c r="P102" s="21" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="Q102" s="33" t="n"/>
-      <c r="R102" s="8" t="n"/>
+      <c r="R102" s="8" t="inlineStr">
+        <is>
+          <t>列表/详情/快捷定位已接入(AlertForm接线+读模型10/10+绑定1/1)；「相关详情」跨界面跳转(进入能源/算法/任务界面)待后续跨界面导航批次</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="72" customHeight="1" s="1">
       <c r="A103" s="24" t="inlineStr">
@@ -12028,11 +12056,15 @@
       </c>
       <c r="P125" s="25" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="Q125" s="34" t="n"/>
-      <c r="R125" s="24" t="n"/>
+      <c r="R125" s="24" t="inlineStr">
+        <is>
+          <t>程序部分已交付：声音五路+主音量乘数/镜头三参数+反转/只读按键(来源InputModule)/显示模式/帧率/基础画质全接线，ISettingsStore(GF.Setting)落盘、世界不暂停；音频资源与动态音频待P8-008/P8-009</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="24" customHeight="1" s="1">
       <c r="A126" s="8" t="inlineStr">
